--- a/artfynd/A 51819-2023 artfynd.xlsx
+++ b/artfynd/A 51819-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51819-2023 artfynd.xlsx
+++ b/artfynd/A 51819-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62025621</v>
+        <v>62025627</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549884.3856166931</v>
+        <v>549991</v>
       </c>
       <c r="R2" t="n">
-        <v>6984044.27247432</v>
+        <v>6983954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025626</v>
+        <v>62025622</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549949.281836189</v>
+        <v>549949</v>
       </c>
       <c r="R3" t="n">
-        <v>6984028.896306038</v>
+        <v>6984029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +850,11 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Hård granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62025627</v>
+        <v>62025623</v>
       </c>
       <c r="B4" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549991.4189695233</v>
+        <v>549949</v>
       </c>
       <c r="R4" t="n">
-        <v>6983953.602201727</v>
+        <v>6984029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +957,11 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Björkhögstubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62025623</v>
+        <v>62025632</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549949.281836189</v>
+        <v>550014</v>
       </c>
       <c r="R5" t="n">
-        <v>6984028.896306038</v>
+        <v>6983896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,21 +1064,11 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,7 +1085,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Mossig mark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62025622</v>
+        <v>62025631</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549949.281836189</v>
+        <v>550014</v>
       </c>
       <c r="R6" t="n">
-        <v>6984028.896306038</v>
+        <v>6983896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,21 +1171,11 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1192,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Hård granlåga</t>
+          <t>Mossig mark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62025625</v>
+        <v>62025619</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549949.281836189</v>
+        <v>549884</v>
       </c>
       <c r="R7" t="n">
-        <v>6984028.896306038</v>
+        <v>6984044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,19 +1278,9 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,12 +1320,7 @@
         <v>62025620</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549884.3856166931</v>
+        <v>549884</v>
       </c>
       <c r="R8" t="n">
-        <v>6984044.27247432</v>
+        <v>6984044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,19 +1385,9 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62025619</v>
+        <v>62025625</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549884.3856166931</v>
+        <v>549949</v>
       </c>
       <c r="R9" t="n">
-        <v>6984044.27247432</v>
+        <v>6984029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,19 +1492,9 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,6 +1528,327 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62025626</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549949</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984029</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62025621</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549884</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984044</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>62025630</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550014</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983896</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51819-2023 artfynd.xlsx
+++ b/artfynd/A 51819-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025627</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025632</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025631</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025619</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025621</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,8 +1904,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>